--- a/artfynd/A 59651-2025 artfynd.xlsx
+++ b/artfynd/A 59651-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130092119</v>
       </c>
       <c r="B2" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>130092120</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>130092115</v>
       </c>
       <c r="B4" t="n">
-        <v>110987</v>
+        <v>110990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>130092121</v>
       </c>
       <c r="B5" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59651-2025 artfynd.xlsx
+++ b/artfynd/A 59651-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130092119</v>
       </c>
       <c r="B2" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>130092120</v>
       </c>
       <c r="B3" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>130092115</v>
       </c>
       <c r="B4" t="n">
-        <v>110990</v>
+        <v>111077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>130092121</v>
       </c>
       <c r="B5" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
